--- a/artfynd/A 7983-2025 artfynd.xlsx
+++ b/artfynd/A 7983-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123322909</v>
       </c>
       <c r="B2" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 7983-2025 artfynd.xlsx
+++ b/artfynd/A 7983-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123322909</v>
       </c>
       <c r="B2" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 7983-2025 artfynd.xlsx
+++ b/artfynd/A 7983-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123322909</v>
       </c>
       <c r="B2" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 7983-2025 artfynd.xlsx
+++ b/artfynd/A 7983-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123322909</v>
       </c>
       <c r="B2" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 7983-2025 artfynd.xlsx
+++ b/artfynd/A 7983-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123322909</v>
       </c>
       <c r="B2" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 7983-2025 artfynd.xlsx
+++ b/artfynd/A 7983-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123322909</v>
       </c>
       <c r="B2" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 7983-2025 artfynd.xlsx
+++ b/artfynd/A 7983-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123322909</v>
       </c>
       <c r="B2" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
